--- a/quiz-template.xlsx
+++ b/quiz-template.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MULTI-CHOICE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SHORT ANSWERS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -663,44 +664,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>How many days are in a week?</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Spell the American word for "colour".</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>color | colour</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -712,23 +675,104 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>How many days are in a week?</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Spell the American word for "colour".</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>color | colour</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>What is the opposite of "hot"?</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>cold</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="130" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>How the Answer column works</t>
+          <t>How this quiz file works</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>The Answer is MATCHED, so it can be a word, a number, True / False / Not Given, or a letter.</t>
+          <t>Two tabs, in this order. Students do MULTI-CHOICE first, then go on to a second page for SHORT ANSWERS. You can leave either tab out.</t>
         </is>
       </c>
     </row>
@@ -738,52 +782,86 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>1. Multiple choice, answer by word or number: type the correct option exactly (Paris, 12). Capitals, spaces and punctuation are ignored; 4.0 equals 4.</t>
+          <t>Tab names: keep the words MULTI-CHOICE and SHORT ANSWERS in the tab names (capitals do not matter).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2. Multiple choice, answer by letter: A, B, C or D.</t>
-        </is>
-      </c>
+      <c r="A5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>3. True / False / Not Given with NO options: leave the options empty and write True, False or Not Given (T, F, NG also work). The buttons are added for you.</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>MULTI-CHOICE tab  (columns: Question, Option A, Option B..., Answer, Points)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>4. True / False with options: fill Option A and B as True and False, then write the answer.</t>
+          <t>1. Answer by word or number: type the correct option exactly (Paris, 12). Capitals, spaces and punctuation are ignored; 4.0 equals 4.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>5. Typed answer (a number or word): leave ALL options empty. Students type it. Spelling must match.</t>
+          <t>2. Answer by letter: A, B, C or D.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>6. Several accepted typed answers: separate them with |  for example  color | colour</t>
+          <t>3. True / False / Not Given with NO options: leave the options empty and write True, False or Not Given (T, F, NG also work). The buttons are added for you.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr"/>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>4. True / False with options: fill Option A and B as True and False, then write the answer.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>SHORT ANSWERS tab  (columns: Question, Answer, Points)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>The student types the answer in a blank box. Capitals do not matter but spelling does, and 4.0 equals 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Several accepted answers: separate them with |   for example   color | colour</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Points is optional (default 1). Delete the blue example rows, then add your own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Using Google Sheets: upload this file to Google Drive, open it and choose File &gt; Save as Google Sheets. Keep both tabs.</t>
         </is>
       </c>
     </row>
